--- a/ONCHO/Impact Assessments/Nigeria/2026/ng_oncho_stop_2605_2_part_stop_bn.xlsx
+++ b/ONCHO/Impact Assessments/Nigeria/2026/ng_oncho_stop_2605_2_part_stop_bn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1935B13A-8FE3-4D41-A540-225968C6B611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C275EB-0FA9-4803-A7F3-59C6B9DBA4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="247">
   <si>
     <t>type</t>
   </si>
@@ -421,12 +421,6 @@
     <t>This ID was alredy used</t>
   </si>
   <si>
-    <t>ng_oncho_stop_2605_2_part_stop_bn</t>
-  </si>
-  <si>
-    <t>(Benue - 2026 May) - 2. Participant Form</t>
-  </si>
-  <si>
     <t>BENUE</t>
   </si>
   <si>
@@ -436,9 +430,6 @@
     <t>APA</t>
   </si>
   <si>
-    <t>BUKURU</t>
-  </si>
-  <si>
     <t>BURUKU</t>
   </si>
   <si>
@@ -457,9 +448,6 @@
     <t>KATSINA-ALA</t>
   </si>
   <si>
-    <t>KONSHISA</t>
-  </si>
-  <si>
     <t>KWANDE</t>
   </si>
   <si>
@@ -478,9 +466,6 @@
     <t>OKPOKWU</t>
   </si>
   <si>
-    <t>OTURKPO</t>
-  </si>
-  <si>
     <t>UKUM</t>
   </si>
   <si>
@@ -493,39 +478,9 @@
     <t>IKPELE</t>
   </si>
   <si>
-    <t>OGBAI</t>
-  </si>
-  <si>
     <t>OWETO</t>
   </si>
   <si>
-    <t>OTURKPO - WETO ROAD</t>
-  </si>
-  <si>
-    <t>AJIO</t>
-  </si>
-  <si>
-    <t>AKOVOLWO</t>
-  </si>
-  <si>
-    <t>ANULE</t>
-  </si>
-  <si>
-    <t>BUTER</t>
-  </si>
-  <si>
-    <t>IHEMBA</t>
-  </si>
-  <si>
-    <t>METU</t>
-  </si>
-  <si>
-    <t>MINDE</t>
-  </si>
-  <si>
-    <t>SUSU</t>
-  </si>
-  <si>
     <t>DOGO</t>
   </si>
   <si>
@@ -541,36 +496,9 @@
     <t>JANGERIGERI</t>
   </si>
   <si>
-    <t>MBAGIR III</t>
-  </si>
-  <si>
-    <t>TYONDUN</t>
-  </si>
-  <si>
     <t>UDEI</t>
   </si>
   <si>
-    <t>YUSHEWE</t>
-  </si>
-  <si>
-    <t>YONOV</t>
-  </si>
-  <si>
-    <t>IBOR</t>
-  </si>
-  <si>
-    <t>UDUDU</t>
-  </si>
-  <si>
-    <t>MBAMTSAR</t>
-  </si>
-  <si>
-    <t>TOR DONGA</t>
-  </si>
-  <si>
-    <t>IKIRIYE ADUM</t>
-  </si>
-  <si>
     <t>AJIO-OBUDU ROAD</t>
   </si>
   <si>
@@ -595,193 +523,259 @@
     <t>USHAI</t>
   </si>
   <si>
-    <t>WAYA</t>
-  </si>
-  <si>
     <t>MBAYONGO LOGO 1</t>
   </si>
   <si>
-    <t>MBAKYONGU</t>
-  </si>
-  <si>
-    <t>IKINGO</t>
-  </si>
-  <si>
-    <t>OJEKWE</t>
-  </si>
-  <si>
-    <t>ICHAMA</t>
-  </si>
-  <si>
-    <t>UGBOKOLO</t>
-  </si>
-  <si>
-    <t>AKPACHI</t>
-  </si>
-  <si>
     <t>BEDE</t>
   </si>
   <si>
-    <t>TSE GYUBA</t>
-  </si>
-  <si>
     <t>AKPAGHER</t>
   </si>
   <si>
-    <t>TYOBAN</t>
-  </si>
-  <si>
     <t>community_id</t>
   </si>
   <si>
-    <t>BEN-AGA_O_001</t>
-  </si>
-  <si>
-    <t>BEN-AGA_O_002</t>
-  </si>
-  <si>
-    <t>BEN-BUK_D_003</t>
-  </si>
-  <si>
-    <t>BEN-GBO_A_004</t>
-  </si>
-  <si>
-    <t>BEN-GUM_T_005</t>
-  </si>
-  <si>
-    <t>BEN-GUM_U_006</t>
-  </si>
-  <si>
-    <t>BEN-GUM_Y_007</t>
-  </si>
-  <si>
-    <t>BEN-GUM_M_008</t>
-  </si>
-  <si>
-    <t>BEN-GWE_Y_009</t>
-  </si>
-  <si>
-    <t>BEN-GWE_I_010</t>
-  </si>
-  <si>
-    <t>BEN-GWE_U_011</t>
-  </si>
-  <si>
-    <t>BEN-KAT_M_012</t>
-  </si>
-  <si>
-    <t>BEN-KAT_T_013</t>
-  </si>
-  <si>
-    <t>BEN-KWA_G_014</t>
-  </si>
-  <si>
-    <t>BEN-KWA_K_015</t>
-  </si>
-  <si>
-    <t>BEN-KWA_M_016</t>
-  </si>
-  <si>
-    <t>BEN-KWA_W_017</t>
-  </si>
-  <si>
-    <t>BEN-KON_I_018</t>
-  </si>
-  <si>
-    <t>BEN-OJU_O_019</t>
-  </si>
-  <si>
-    <t>BEN-OKP_I_020</t>
-  </si>
-  <si>
-    <t>BEN-OKP_U_021</t>
-  </si>
-  <si>
-    <t>BEN-OTU_A_022</t>
-  </si>
-  <si>
-    <t>BEN-UKU_B_023</t>
-  </si>
-  <si>
-    <t>BEN-UKU_T_024</t>
-  </si>
-  <si>
-    <t>BEN-USH_A_025</t>
-  </si>
-  <si>
-    <t>BEN-USH_T_026</t>
-  </si>
-  <si>
-    <t>BEN-BUR_U_027</t>
-  </si>
-  <si>
-    <t>BEN-MAK_M_028</t>
-  </si>
-  <si>
-    <t>BEN-LOG_M_029</t>
-  </si>
-  <si>
-    <t>BEN-OBI_I_030</t>
-  </si>
-  <si>
-    <t>BEN-AGA_A_031</t>
-  </si>
-  <si>
-    <t>BEN-AGA_I_032</t>
-  </si>
-  <si>
-    <t>BEN-APA_O_033</t>
-  </si>
-  <si>
-    <t>BEN-BEN_A_034</t>
-  </si>
-  <si>
-    <t>BEN-BEN_A_035</t>
-  </si>
-  <si>
-    <t>BEN-BEN_A_036</t>
-  </si>
-  <si>
-    <t>BEN-BEN_B_037</t>
-  </si>
-  <si>
-    <t>BEN-BEN_I_038</t>
-  </si>
-  <si>
-    <t>BEN-BEN_K_039</t>
-  </si>
-  <si>
-    <t>BEN-BEN_M_040</t>
-  </si>
-  <si>
-    <t>BEN-BEN_M_041</t>
-  </si>
-  <si>
-    <t>BEN-BEN_S_042</t>
-  </si>
-  <si>
-    <t>BEN-GUM_B_043</t>
-  </si>
-  <si>
-    <t>BEN-GUM_J_044</t>
-  </si>
-  <si>
-    <t>BEN-KWA_A_045</t>
-  </si>
-  <si>
-    <t>BEN-KWA_I_046</t>
-  </si>
-  <si>
-    <t>BEN-KWA_K_047</t>
-  </si>
-  <si>
-    <t>BEN-KWA_T_048</t>
-  </si>
-  <si>
-    <t>BEN-KWA_U_049</t>
-  </si>
-  <si>
     <t>ng2605st</t>
+  </si>
+  <si>
+    <t>KONSHISHA</t>
+  </si>
+  <si>
+    <t>OTUKPO</t>
+  </si>
+  <si>
+    <t>OGBAI (IKPELE)</t>
+  </si>
+  <si>
+    <t>OTURKPO - WETO ROAD(OZANTELE)</t>
+  </si>
+  <si>
+    <t>GBAJIMBA IDP CAMP</t>
+  </si>
+  <si>
+    <t>IDP CAMP 1 DAUDU</t>
+  </si>
+  <si>
+    <t>IDP CAMP 2 DAUDU (UIKPAM)</t>
+  </si>
+  <si>
+    <t>IDP CAMP 3 DAUDU</t>
+  </si>
+  <si>
+    <t>TYOHEMBE</t>
+  </si>
+  <si>
+    <t>UNYIANDE</t>
+  </si>
+  <si>
+    <t>ANCHIHA</t>
+  </si>
+  <si>
+    <t>MBAAGIR</t>
+  </si>
+  <si>
+    <t>IDP CAMP NAKA</t>
+  </si>
+  <si>
+    <t>NAGI</t>
+  </si>
+  <si>
+    <t>NAKA</t>
+  </si>
+  <si>
+    <t>AMAAFU</t>
+  </si>
+  <si>
+    <t>JOO-MBATYOUGH</t>
+  </si>
+  <si>
+    <t>IKPEAKOR</t>
+  </si>
+  <si>
+    <t>REFUGEE SETTLEMENT (IKYOGEN)</t>
+  </si>
+  <si>
+    <t>IDP CAMP ANYIIN</t>
+  </si>
+  <si>
+    <t>MINDI</t>
+  </si>
+  <si>
+    <t>ADAKA</t>
+  </si>
+  <si>
+    <t>IDP CAMP ABAGANA</t>
+  </si>
+  <si>
+    <t>EKINGO</t>
+  </si>
+  <si>
+    <t>OJOKWE</t>
+  </si>
+  <si>
+    <t>ICHAMA CENTRAL</t>
+  </si>
+  <si>
+    <t>ODESSASSA I</t>
+  </si>
+  <si>
+    <t>AKPACHI UGBOJU</t>
+  </si>
+  <si>
+    <t>TSE GUBE</t>
+  </si>
+  <si>
+    <t>AKERIOR</t>
+  </si>
+  <si>
+    <t>BEN_AGA_O_001</t>
+  </si>
+  <si>
+    <t>BEN_AGA_A_002</t>
+  </si>
+  <si>
+    <t>BEN_AGA_I_003</t>
+  </si>
+  <si>
+    <t>BEN_AGA_O_004</t>
+  </si>
+  <si>
+    <t>BEN_APA_O_001</t>
+  </si>
+  <si>
+    <t>BEN_BUR_D_001</t>
+  </si>
+  <si>
+    <t>BEN_BUR_U_002</t>
+  </si>
+  <si>
+    <t>BEN_GBO_A_001</t>
+  </si>
+  <si>
+    <t>BEN_GUM_B_001</t>
+  </si>
+  <si>
+    <t>BEN_GUM_J_002</t>
+  </si>
+  <si>
+    <t>BEN_GUM_I_003</t>
+  </si>
+  <si>
+    <t>BEN_GUM_T_004</t>
+  </si>
+  <si>
+    <t>BEN_GUM_I_005</t>
+  </si>
+  <si>
+    <t>BEN_GUM_G_006</t>
+  </si>
+  <si>
+    <t>BEN_GUM_U_007</t>
+  </si>
+  <si>
+    <t>BEN_GUM_U_008</t>
+  </si>
+  <si>
+    <t>BEN_GUM_I_009</t>
+  </si>
+  <si>
+    <t>BEN_GWE_M_001</t>
+  </si>
+  <si>
+    <t>BEN_GWE_A_002</t>
+  </si>
+  <si>
+    <t>BEN_GWE_N_003</t>
+  </si>
+  <si>
+    <t>BEN_GWE_N_004</t>
+  </si>
+  <si>
+    <t>BEN_GWE_I_005</t>
+  </si>
+  <si>
+    <t>BEN_KAT_J_001</t>
+  </si>
+  <si>
+    <t>BEN_KAT_A_002</t>
+  </si>
+  <si>
+    <t>BEN_KON_I_001</t>
+  </si>
+  <si>
+    <t>BEN_KWA_G_001</t>
+  </si>
+  <si>
+    <t>BEN_KWA_K_002</t>
+  </si>
+  <si>
+    <t>BEN_KWA_A_003</t>
+  </si>
+  <si>
+    <t>BEN_KWA_A_004</t>
+  </si>
+  <si>
+    <t>BEN_KWA_I_005</t>
+  </si>
+  <si>
+    <t>BEN_KWA_K_006</t>
+  </si>
+  <si>
+    <t>BEN_KWA_T_007</t>
+  </si>
+  <si>
+    <t>BEN_KWA_U_008</t>
+  </si>
+  <si>
+    <t>BEN_KWA_R_009</t>
+  </si>
+  <si>
+    <t>BEN_LOG_M_001</t>
+  </si>
+  <si>
+    <t>BEN_LOG_M_002</t>
+  </si>
+  <si>
+    <t>BEN_LOG_I_003</t>
+  </si>
+  <si>
+    <t>BEN_MAK_I_001</t>
+  </si>
+  <si>
+    <t>BEN_MAK_A_002</t>
+  </si>
+  <si>
+    <t>BEN_OBI_E_001</t>
+  </si>
+  <si>
+    <t>BEN_OJU_O_001</t>
+  </si>
+  <si>
+    <t>BEN_OKP_O_001</t>
+  </si>
+  <si>
+    <t>BEN_OKP_I_002</t>
+  </si>
+  <si>
+    <t>BEN_OTU_A_001</t>
+  </si>
+  <si>
+    <t>BEN_UKU_B_001</t>
+  </si>
+  <si>
+    <t>BEN_UKU_T_002</t>
+  </si>
+  <si>
+    <t>BEN_USH_A_001</t>
+  </si>
+  <si>
+    <t>BEN_USH_M_002</t>
+  </si>
+  <si>
+    <t>ng_oncho_stop_2605_2_part_stop_bn_v2</t>
+  </si>
+  <si>
+    <t>(Benue - 2026 May) - 2. Participant Form V2</t>
   </si>
 </sst>
 </file>
@@ -1607,7 +1601,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>98</v>
@@ -2237,10 +2231,10 @@
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:6" customFormat="1"/>
@@ -2249,13 +2243,13 @@
         <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:4" customFormat="1">
@@ -2263,13 +2257,13 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:4" customFormat="1">
@@ -2277,13 +2271,13 @@
         <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:4" customFormat="1">
@@ -2291,13 +2285,13 @@
         <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:4" customFormat="1">
@@ -2305,13 +2299,13 @@
         <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:4" customFormat="1">
@@ -2319,13 +2313,13 @@
         <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:4" customFormat="1">
@@ -2333,13 +2327,13 @@
         <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:4" customFormat="1">
@@ -2347,13 +2341,13 @@
         <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:4" customFormat="1">
@@ -2361,13 +2355,13 @@
         <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:4" customFormat="1">
@@ -2375,13 +2369,13 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:4" customFormat="1">
@@ -2389,13 +2383,13 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:4" customFormat="1">
@@ -2403,13 +2397,13 @@
         <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:4" customFormat="1">
@@ -2417,13 +2411,13 @@
         <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:4" customFormat="1">
@@ -2431,13 +2425,13 @@
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:4" customFormat="1">
@@ -2445,13 +2439,13 @@
         <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:4" customFormat="1">
@@ -2459,13 +2453,13 @@
         <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="D31" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:4" customFormat="1">
@@ -2473,13 +2467,13 @@
         <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:5" customFormat="1">
@@ -2487,56 +2481,56 @@
         <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D33" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" customFormat="1">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" t="s">
-        <v>148</v>
-      </c>
-      <c r="C34" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" t="s">
-        <v>130</v>
-      </c>
-    </row>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" customFormat="1"/>
     <row r="35" spans="1:5" customFormat="1">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C35" t="s">
-        <v>149</v>
-      </c>
-      <c r="D35" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" customFormat="1"/>
+        <v>145</v>
+      </c>
+      <c r="E35" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" customFormat="1">
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" t="s">
+        <v>129</v>
+      </c>
+    </row>
     <row r="37" spans="1:5" customFormat="1">
       <c r="A37" t="s">
         <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="E37" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:5" customFormat="1">
@@ -2544,13 +2538,13 @@
         <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E38" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:5" customFormat="1">
@@ -2558,13 +2552,13 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="E39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:5" customFormat="1">
@@ -2572,10 +2566,10 @@
         <v>68</v>
       </c>
       <c r="B40" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E40" t="s">
         <v>131</v>
@@ -2586,13 +2580,13 @@
         <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:5" customFormat="1">
@@ -2600,13 +2594,13 @@
         <v>68</v>
       </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C42" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E42" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:5" customFormat="1">
@@ -2614,13 +2608,13 @@
         <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E43" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:5" customFormat="1">
@@ -2628,13 +2622,13 @@
         <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="E44" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:5" customFormat="1">
@@ -2642,13 +2636,13 @@
         <v>68</v>
       </c>
       <c r="B45" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="E45" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:5" customFormat="1">
@@ -2656,13 +2650,13 @@
         <v>68</v>
       </c>
       <c r="B46" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E46" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" spans="1:5" customFormat="1">
@@ -2670,13 +2664,13 @@
         <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="E47" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:5" customFormat="1">
@@ -2684,13 +2678,13 @@
         <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E48" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:5" customFormat="1">
@@ -2698,13 +2692,13 @@
         <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E49" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:5" customFormat="1">
@@ -2712,13 +2706,13 @@
         <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C50" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E50" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:5" customFormat="1">
@@ -2726,10 +2720,10 @@
         <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C51" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="E51" t="s">
         <v>133</v>
@@ -2740,10 +2734,10 @@
         <v>68</v>
       </c>
       <c r="B52" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C52" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="E52" t="s">
         <v>134</v>
@@ -2754,13 +2748,13 @@
         <v>68</v>
       </c>
       <c r="B53" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C53" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="E53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:5" customFormat="1">
@@ -2768,13 +2762,13 @@
         <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="E54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" spans="1:5" customFormat="1">
@@ -2782,13 +2776,13 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C55" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E55" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:5" customFormat="1">
@@ -2796,13 +2790,13 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C56" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="E56" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:5" customFormat="1">
@@ -2810,10 +2804,10 @@
         <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C57" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="E57" t="s">
         <v>136</v>
@@ -2824,10 +2818,10 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C58" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E58" t="s">
         <v>136</v>
@@ -2838,13 +2832,13 @@
         <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C59" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="E59" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:5" customFormat="1">
@@ -2852,10 +2846,10 @@
         <v>68</v>
       </c>
       <c r="B60" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="E60" t="s">
         <v>137</v>
@@ -2866,13 +2860,13 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="C61" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="E61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:5" customFormat="1">
@@ -2880,13 +2874,13 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="C62" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="E62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:5" customFormat="1">
@@ -2894,13 +2888,13 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="C63" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="E63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:5" customFormat="1">
@@ -2908,13 +2902,13 @@
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="C64" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="E64" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:5" customFormat="1">
@@ -2922,13 +2916,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="E65" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:5" customFormat="1">
@@ -2936,13 +2930,13 @@
         <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C66" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E66" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67" spans="1:5" customFormat="1">
@@ -2950,13 +2944,13 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="C67" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:5" customFormat="1">
@@ -2964,13 +2958,13 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C68" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="E68" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:5" customFormat="1">
@@ -2978,13 +2972,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C69" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:5" customFormat="1">
@@ -2992,13 +2986,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="C70" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="E70" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" spans="1:5" customFormat="1">
@@ -3006,13 +3000,13 @@
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C71" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E71" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:5" customFormat="1">
@@ -3020,13 +3014,13 @@
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C72" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E72" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:5" customFormat="1">
@@ -3034,13 +3028,13 @@
         <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C73" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E73" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:5" customFormat="1">
@@ -3048,13 +3042,13 @@
         <v>68</v>
       </c>
       <c r="B74" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C74" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E74" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:5" customFormat="1">
@@ -3062,13 +3056,13 @@
         <v>68</v>
       </c>
       <c r="B75" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C75" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E75" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:5" customFormat="1">
@@ -3076,13 +3070,13 @@
         <v>68</v>
       </c>
       <c r="B76" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E76" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="1:5" customFormat="1">
@@ -3090,13 +3084,13 @@
         <v>68</v>
       </c>
       <c r="B77" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C77" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E77" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78" spans="1:5" customFormat="1">
@@ -3104,13 +3098,13 @@
         <v>68</v>
       </c>
       <c r="B78" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C78" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E78" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:5" customFormat="1">
@@ -3118,13 +3112,13 @@
         <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="C79" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E79" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:5" customFormat="1">
@@ -3132,13 +3126,13 @@
         <v>68</v>
       </c>
       <c r="B80" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C80" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E80" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81" spans="1:6" customFormat="1">
@@ -3146,13 +3140,13 @@
         <v>68</v>
       </c>
       <c r="B81" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C81" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E81" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="1:6" customFormat="1">
@@ -3160,235 +3154,235 @@
         <v>68</v>
       </c>
       <c r="B82" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="C82" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="E82" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" customFormat="1">
-      <c r="A83" t="s">
-        <v>68</v>
-      </c>
-      <c r="B83" t="s">
-        <v>195</v>
-      </c>
-      <c r="C83" t="s">
-        <v>195</v>
-      </c>
-      <c r="E83" t="s">
-        <v>148</v>
-      </c>
-    </row>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" customFormat="1"/>
     <row r="84" spans="1:6" customFormat="1">
       <c r="A84" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="B84" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C84" t="s">
-        <v>196</v>
-      </c>
-      <c r="E84" t="s">
-        <v>149</v>
+        <v>197</v>
+      </c>
+      <c r="F84" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="85" spans="1:6" customFormat="1">
       <c r="A85" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="B85" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C85" t="s">
-        <v>197</v>
-      </c>
-      <c r="E85" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" customFormat="1"/>
+        <v>198</v>
+      </c>
+      <c r="F85" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" customFormat="1">
+      <c r="A86" t="s">
+        <v>165</v>
+      </c>
+      <c r="B86" t="s">
+        <v>199</v>
+      </c>
+      <c r="C86" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" t="s">
+        <v>146</v>
+      </c>
+    </row>
     <row r="87" spans="1:6" customFormat="1">
       <c r="A87" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C87" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F87" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:6" customFormat="1">
       <c r="A88" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B88" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C88" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F88" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:6" customFormat="1">
       <c r="A89" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B89" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C89" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F89" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:6" customFormat="1">
       <c r="A90" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B90" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C90" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F90" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:6" customFormat="1">
       <c r="A91" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B91" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F91" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" spans="1:6" customFormat="1">
       <c r="A92" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B92" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C92" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F92" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:6" customFormat="1">
       <c r="A93" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F93" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:6" customFormat="1">
       <c r="A94" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F94" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="1:6" customFormat="1">
       <c r="A95" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B95" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C95" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F95" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="96" spans="1:6" customFormat="1">
       <c r="A96" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B96" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C96" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F96" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97" spans="1:6" customFormat="1">
       <c r="A97" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B97" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C97" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F97" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98" spans="1:6" customFormat="1">
       <c r="A98" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F98" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="99" spans="1:6" customFormat="1">
       <c r="A99" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B99" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C99" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F99" t="s">
         <v>176</v>
@@ -3396,508 +3390,456 @@
     </row>
     <row r="100" spans="1:6" customFormat="1">
       <c r="A100" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F100" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101" spans="1:6" customFormat="1">
       <c r="A101" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B101" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C101" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F101" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="102" spans="1:6" customFormat="1">
       <c r="A102" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B102" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C102" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F102" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103" spans="1:6" customFormat="1">
       <c r="A103" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B103" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C103" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F103" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:6" customFormat="1">
       <c r="A104" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B104" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C104" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F104" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:6" customFormat="1">
       <c r="A105" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B105" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C105" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F105" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="106" spans="1:6" customFormat="1">
       <c r="A106" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B106" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C106" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F106" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="107" spans="1:6" customFormat="1">
       <c r="A107" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B107" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C107" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F107" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="108" spans="1:6" customFormat="1">
       <c r="A108" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B108" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C108" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F108" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:6" customFormat="1">
       <c r="A109" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B109" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C109" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F109" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
     </row>
     <row r="110" spans="1:6" customFormat="1">
       <c r="A110" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B110" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C110" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F110" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
     </row>
     <row r="111" spans="1:6" customFormat="1">
       <c r="A111" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B111" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C111" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F111" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112" spans="1:6" customFormat="1">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:6" customFormat="1">
       <c r="A113" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B113" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C113" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F113" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:6" customFormat="1">
       <c r="A114" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B114" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C114" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F114" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
     </row>
     <row r="115" spans="1:6" customFormat="1">
       <c r="A115" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B115" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C115" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F115" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116" spans="1:6" customFormat="1">
       <c r="A116" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B116" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C116" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F116" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
     </row>
     <row r="117" spans="1:6" customFormat="1">
       <c r="A117" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B117" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C117" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F117" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
     </row>
     <row r="118" spans="1:6" customFormat="1">
       <c r="A118" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B118" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C118" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F118" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="119" spans="1:6" customFormat="1">
       <c r="A119" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B119" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C119" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F119" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
     </row>
     <row r="120" spans="1:6" customFormat="1">
       <c r="A120" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B120" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C120" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F120" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
     </row>
     <row r="121" spans="1:6" customFormat="1">
       <c r="A121" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B121" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C121" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F121" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
     </row>
     <row r="122" spans="1:6" customFormat="1">
       <c r="A122" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F122" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
     </row>
     <row r="123" spans="1:6" customFormat="1">
       <c r="A123" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B123" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C123" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F123" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124" spans="1:6" customFormat="1">
       <c r="A124" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B124" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C124" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F124" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" spans="1:6" customFormat="1">
       <c r="A125" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B125" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C125" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F125" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
     </row>
     <row r="126" spans="1:6" customFormat="1">
       <c r="A126" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B126" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C126" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F126" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="127" spans="1:6" customFormat="1">
       <c r="A127" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B127" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C127" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F127" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="1:6" customFormat="1">
       <c r="A128" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B128" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C128" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F128" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="129" spans="1:6" customFormat="1">
       <c r="A129" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B129" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C129" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F129" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
     </row>
     <row r="130" spans="1:6" customFormat="1">
       <c r="A130" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B130" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C130" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F130" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
     </row>
     <row r="131" spans="1:6" customFormat="1">
       <c r="A131" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B131" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C131" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F131" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" customFormat="1">
-      <c r="A132" t="s">
-        <v>198</v>
-      </c>
-      <c r="B132" t="s">
-        <v>244</v>
-      </c>
-      <c r="C132" t="s">
-        <v>244</v>
-      </c>
-      <c r="F132" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" customFormat="1">
-      <c r="A133" t="s">
-        <v>198</v>
-      </c>
-      <c r="B133" t="s">
-        <v>245</v>
-      </c>
-      <c r="C133" t="s">
-        <v>245</v>
-      </c>
-      <c r="F133" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" customFormat="1">
-      <c r="A134" t="s">
-        <v>198</v>
-      </c>
-      <c r="B134" t="s">
-        <v>246</v>
-      </c>
-      <c r="C134" t="s">
-        <v>246</v>
-      </c>
-      <c r="F134" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" customFormat="1">
-      <c r="A135" t="s">
-        <v>198</v>
-      </c>
-      <c r="B135" t="s">
-        <v>247</v>
-      </c>
-      <c r="C135" t="s">
-        <v>247</v>
-      </c>
-      <c r="F135" t="s">
-        <v>185</v>
-      </c>
-    </row>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" customFormat="1"/>
+    <row r="133" spans="1:6" customFormat="1"/>
+    <row r="134" spans="1:6" customFormat="1"/>
+    <row r="135" spans="1:6" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3926,10 +3868,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>129</v>
+        <v>246</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>128</v>
+        <v>245</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>66</v>
